--- a/docs/downloads/AAU_Research_Tracker.xlsx
+++ b/docs/downloads/AAU_Research_Tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260914-083516</t>
+          <t>20260921-083647</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T08:41:01</t>
+          <t>2026-09-21T08:36:57</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/AAU_Research_Tracker.xlsx
+++ b/docs/downloads/AAU_Research_Tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260928-092403</t>
+          <t>20261005-100246</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-28T09:29:54</t>
+          <t>2026-10-05T10:02:56</t>
         </is>
       </c>
     </row>
@@ -74713,7 +74713,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>could not verify: no OpenAlex record</t>
+          <t>no author printed an Al Ain University address</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/AAU_Research_Tracker.xlsx
+++ b/docs/downloads/AAU_Research_Tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261005-100246</t>
+          <t>20261012-101659</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05T10:02:56</t>
+          <t>2026-10-12T10:17:08</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/AAU_Research_Tracker.xlsx
+++ b/docs/downloads/AAU_Research_Tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20261012-101659</t>
+          <t>20261019-083110</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12T10:17:08</t>
+          <t>2026-10-19T08:31:20</t>
         </is>
       </c>
     </row>
